--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_a_2018_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_a_2018_nuble.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:50</t>
+    <t xml:space="preserve">2026-09-24 00:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -825,10 +825,10 @@
         <v>21</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.34</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0.02</v>
@@ -848,13 +848,13 @@
         <v>21</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="16">
@@ -874,7 +874,7 @@
         <v>-0.36</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0.03</v>
@@ -894,13 +894,13 @@
         <v>21</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="18">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_a_2018_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_a_2018_nuble.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:41</t>
+    <t xml:space="preserve">2026-10-01 23:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_a_2018_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_a_2018_nuble.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:16</t>
+    <t xml:space="preserve">2026-10-05 19:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
